--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.56063081467107</v>
+        <v>9.19110250738405</v>
       </c>
       <c r="D2" t="n">
-        <v>56.53469662279877</v>
+        <v>9.1868882012048</v>
       </c>
       <c r="E2" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F2" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.37308536874441</v>
+        <v>10.94812637242097</v>
       </c>
       <c r="D3" t="n">
-        <v>67.3598992567938</v>
+        <v>10.94598362922899</v>
       </c>
       <c r="E3" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F3" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.20438204737</v>
+        <v>8.483212082697626</v>
       </c>
       <c r="D4" t="n">
-        <v>52.17059491935851</v>
+        <v>8.47772167439576</v>
       </c>
       <c r="E4" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F4" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.37959107846972</v>
+        <v>9.48668355025133</v>
       </c>
       <c r="D5" t="n">
-        <v>58.36596450800306</v>
+        <v>9.484469232550497</v>
       </c>
       <c r="E5" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F5" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>83.70202748465903</v>
+        <v>13.60157946625709</v>
       </c>
       <c r="D6" t="n">
-        <v>83.67252607278621</v>
+        <v>13.59678548682776</v>
       </c>
       <c r="E6" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F6" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.43278220973082</v>
+        <v>8.032827109081259</v>
       </c>
       <c r="D7" t="n">
-        <v>49.41271849446067</v>
+        <v>8.02956675534986</v>
       </c>
       <c r="E7" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F7" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.28668067505473</v>
+        <v>7.359085609696394</v>
       </c>
       <c r="D8" t="n">
-        <v>45.27012361943984</v>
+        <v>7.356395088158974</v>
       </c>
       <c r="E8" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F8" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.68326175931546</v>
+        <v>9.536030035888762</v>
       </c>
       <c r="D9" t="n">
-        <v>58.68094345507262</v>
+        <v>9.5356533114493</v>
       </c>
       <c r="E9" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F9" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.42078813925683</v>
+        <v>6.893378072629234</v>
       </c>
       <c r="D10" t="n">
-        <v>42.41462273263342</v>
+        <v>6.892376194052931</v>
       </c>
       <c r="E10" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F10" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>65.46038392553874</v>
+        <v>10.63731238790004</v>
       </c>
       <c r="D11" t="n">
-        <v>65.43465431247029</v>
+        <v>10.63313132577642</v>
       </c>
       <c r="E11" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F11" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>55.15084486352922</v>
+        <v>8.962012290323498</v>
       </c>
       <c r="D12" t="n">
-        <v>55.12594773810917</v>
+        <v>8.957966507442741</v>
       </c>
       <c r="E12" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F12" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>39.25997735871484</v>
+        <v>6.379746320791162</v>
       </c>
       <c r="D13" t="n">
-        <v>39.23644049327697</v>
+        <v>6.375921580157509</v>
       </c>
       <c r="E13" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F13" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.72929779723507</v>
+        <v>6.456010892050699</v>
       </c>
       <c r="D14" t="n">
-        <v>39.73848906843896</v>
+        <v>6.457504473621331</v>
       </c>
       <c r="E14" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F14" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.71138472456644</v>
+        <v>8.728100017742046</v>
       </c>
       <c r="D15" t="n">
-        <v>53.72588937647807</v>
+        <v>8.730457023677685</v>
       </c>
       <c r="E15" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F15" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>62.39142313104158</v>
+        <v>10.13860625879426</v>
       </c>
       <c r="D16" t="n">
-        <v>62.38587536542153</v>
+        <v>10.137704746881</v>
       </c>
       <c r="E16" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F16" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>60.60463200739049</v>
+        <v>9.848252701200954</v>
       </c>
       <c r="D17" t="n">
-        <v>60.60690676169419</v>
+        <v>9.848622348775306</v>
       </c>
       <c r="E17" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F17" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>91.66149484619073</v>
+        <v>14.89499291250599</v>
       </c>
       <c r="D18" t="n">
-        <v>91.67192938543405</v>
+        <v>14.89668852513303</v>
       </c>
       <c r="E18" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F18" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>94.98858075024492</v>
+        <v>15.4356443719148</v>
       </c>
       <c r="D19" t="n">
-        <v>95.00208791919692</v>
+        <v>15.4378392868695</v>
       </c>
       <c r="E19" t="n">
-        <v>15.80514703926237</v>
+        <v>2.568336393880134</v>
       </c>
       <c r="F19" t="n">
-        <v>15.80900430184863</v>
+        <v>2.568963199050402</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
